--- a/artfynd/A 27014-2026 artfynd.xlsx
+++ b/artfynd/A 27014-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91259847</v>
+        <v>130779713</v>
       </c>
       <c r="B2" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,31 +708,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stormossen, Gstr</t>
+          <t>Avesta, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587379.0791769982</v>
+        <v>587393</v>
       </c>
       <c r="R2" t="n">
-        <v>6693823.024035558</v>
+        <v>6693740</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,22 +754,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-29</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-30</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spillning på väg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,44 +789,48 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>JPN0048 Stormossen fågel 2024</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130779713</v>
+        <v>91259847</v>
       </c>
       <c r="B3" t="n">
-        <v>57073</v>
+        <v>56816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,26 +838,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Avesta, Gstr</t>
+          <t>Stormossen, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587393</v>
+        <v>587379</v>
       </c>
       <c r="R3" t="n">
-        <v>6693740</v>
+        <v>6693823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,27 +889,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2020-07-29</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2020-07-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spillning på väg</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,19 +919,15 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>JPN0048 Stormossen fågel 2024</t>
-        </is>
-      </c>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27014-2026 artfynd.xlsx
+++ b/artfynd/A 27014-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>JPN0048 Stormossen fågel 2024</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130779713</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -928,8 +938,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91259847</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>